--- a/EXCEL/Data/særydelser-og-merarbejde/merarbejde_klassificering.xlsx
+++ b/EXCEL/Data/særydelser-og-merarbejde/merarbejde_klassificering.xlsx
@@ -34,7 +34,7 @@
     <t>Datasæt 02 2025</t>
   </si>
   <si>
-    <t>Kørsel 10.4.2026 12.19.14</t>
+    <t>Kørsel 14.4.2026 12.27.09</t>
   </si>
   <si>
     <t/>
